--- a/data/b2_candoi/B2 Candói 05-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 05-2026.xlsx
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1664.97</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="3">
@@ -4828,25 +4828,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>58392.54</v>
+        <v>57728.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1125.13</v>
+        <v>1544.08</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3466.89</v>
+        <v>3279.91</v>
       </c>
     </row>
     <row r="7">
@@ -4896,11 +4896,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1404.35</v>
+        <v>1056.17</v>
       </c>
     </row>
     <row r="8">
@@ -4918,97 +4918,97 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1027.48</v>
+        <v>1114.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8507.450000000001</v>
+        <v>1091.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>907.52</v>
+        <v>958.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2225.7</v>
+        <v>8275.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3429.05</v>
+        <v>984.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1946.58</v>
+        <v>3604.37</v>
       </c>
     </row>
     <row r="14">
@@ -5026,61 +5026,61 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20496.61</v>
+        <v>20256.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3313.89</v>
+        <v>694.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>7590</v>
+        <v>3283.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1776.19</v>
+        <v>7590</v>
       </c>
     </row>
     <row r="18">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3375.28</v>
+        <v>3394.16</v>
       </c>
     </row>
   </sheetData>
